--- a/etf_holdings/2026-09-29_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-29_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,29 +464,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(100,000)、00993A(3,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00991A(-310,000)、00982A(-80,000)、00403A(-100,000)</t>
+          <t>00985A(-78,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -504,19 +504,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00982A(-5,000)、00403A(-170,000)</t>
+          <t>00403A(-36,000)、00400A(-18,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,28 +529,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00991A(100,000)、00993A(3,000)</t>
+          <t>00991A(100,000)、00993A(7,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00985A(-78,000)</t>
+          <t>00985A(-64,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -559,28 +559,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00993A(1,000)</t>
+          <t>00991A(300,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00403A(-36,000)、00400A(-18,000)</t>
+          <t>00992A(-1,800,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -589,54 +589,54 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00993A(9,000)</t>
+          <t>00993A(23,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00981A(-1,000,000)、00982A(-30,000)</t>
+          <t>00991A(-700,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00991A(100,000)、00993A(7,000)</t>
+          <t>00991A(200,000)、00993A(2,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00985A(-64,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00991A(300,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00992A(-1,800,000)</t>
+          <t>00991A(-310,000)、00403A(-100,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -679,24 +679,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00993A(9,000)</t>
+          <t>00993A(1,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00982A(-14,000)</t>
+          <t>00403A(-170,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -709,24 +709,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00993A(103,000)</t>
+          <t>00991A(50,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00982A(-29,000)</t>
+          <t>00400A(-29,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -739,24 +739,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00993A(23,000)</t>
+          <t>00993A(6,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00991A(-700,000)</t>
+          <t>00403A(-350,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00991A(200,000)、00993A(2,000)</t>
+          <t>00991A(100,000)、00993A(27,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -781,12 +781,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -794,29 +794,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>00985A(新納入)、00993A(3,000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00982A(-12,000)、00985A(-192,000)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -829,24 +829,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>00993A(1,000)</t>
+          <t>00993A(9,000)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>00982A(-2,000)</t>
+          <t>00981A(-1,000,000)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -859,24 +859,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>00993A(8,000)</t>
+          <t>00993A(2,000)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>00982A(-164,000)</t>
+          <t>00991A(-100,000)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -884,29 +884,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>00991A(50,000)</t>
+          <t>00993A(39,000)、00400A(1,244,000)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>00400A(-29,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -919,190 +919,10 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>00993A(6,000)</t>
+          <t>00403A(75,000)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>00403A(-350,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>00991A(100,000)、00993A(27,000)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>雙鴻</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>00985A(新納入)、00993A(3,000)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>00993A(2,000)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>00991A(-100,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>00981A(265,000)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>00982A(-3,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>00993A(39,000)、00400A(1,244,000)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>00403A(75,000)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
         <is>
           <t>00985A(-21,000)</t>
         </is>

--- a/etf_holdings/2026-09-29_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-29_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,29 +464,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00991A(100,000)、00993A(3,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00985A(-78,000)</t>
+          <t>00991A(-310,000)、00982A(-80,000)、00403A(-100,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -504,19 +504,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00403A(-36,000)、00400A(-18,000)</t>
+          <t>00982A(-5,000)、00403A(-170,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,28 +529,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00991A(100,000)、00993A(7,000)</t>
+          <t>00993A(1,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00985A(-64,000)</t>
+          <t>00403A(-36,000)、00400A(-18,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -559,24 +559,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00991A(300,000)</t>
+          <t>00993A(9,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00992A(-1,800,000)</t>
+          <t>00981A(-1,000,000)、00982A(-30,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,24 +589,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00993A(23,000)</t>
+          <t>00991A(300,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00991A(-700,000)</t>
+          <t>00992A(-1,800,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00991A(200,000)、00993A(2,000)</t>
+          <t>00993A(9,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00982A(-14,000)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(103,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00991A(-310,000)、00403A(-100,000)</t>
+          <t>00982A(-29,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -679,24 +679,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00993A(1,000)</t>
+          <t>00993A(23,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00403A(-170,000)</t>
+          <t>00991A(-700,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -704,29 +704,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00991A(50,000)</t>
+          <t>00991A(200,000)、00993A(2,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00400A(-29,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -739,24 +739,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00993A(6,000)</t>
+          <t>00993A(1,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>00403A(-350,000)</t>
+          <t>00982A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -764,29 +764,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00991A(100,000)、00993A(27,000)</t>
+          <t>00993A(8,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00982A(-164,000)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -794,29 +794,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>00985A(新納入)、00993A(3,000)</t>
+          <t>00991A(50,000)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00400A(-29,000)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -829,24 +829,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>00993A(9,000)</t>
+          <t>00993A(6,000)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>00981A(-1,000,000)</t>
+          <t>00403A(-350,000)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -854,29 +854,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>00993A(2,000)</t>
+          <t>00991A(100,000)、00993A(27,000)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>00991A(-100,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -889,7 +889,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>00993A(39,000)、00400A(1,244,000)</t>
+          <t>00991A(100,000)、00993A(3,000)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -919,12 +919,102 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>00403A(75,000)</t>
+          <t>00993A(2,000)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>00985A(-21,000)</t>
+          <t>00991A(-100,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>00981A(265,000)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>00982A(-3,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>00993A(39,000)、00400A(1,244,000)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>00991A(100,000)、00993A(7,000)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
